--- a/experiments/20250711_mutidrugs/iteration_0/raw_data/raw_absorbance_i0.xlsx
+++ b/experiments/20250711_mutidrugs/iteration_0/raw_data/raw_absorbance_i0.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zeqing/0_Github/drug_surfactant/experiments/20250711_mutidrugs/iteration_0/raw_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Surfactant\0711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B1118C-ED35-814F-81A7-B6CF5F2828D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B1DEAD3-7426-42B2-9B9A-A6284C010418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1840" yWindow="1840" windowWidth="25480" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="9528" windowHeight="10356"/>
   </bookViews>
   <sheets>
     <sheet name="Plate 2 - Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MethodPointer1">-1571030480</definedName>
-    <definedName name="MethodPointer2">633</definedName>
+    <definedName name="MethodPointer1">1830548720</definedName>
+    <definedName name="MethodPointer2">396</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
     <t>Experiment File Path:</t>
   </si>
   <si>
-    <t>D:\Surfactant\0627\ot-0.xpt</t>
+    <t>D:\Surfactant\0711\ot-0.xpt</t>
   </si>
   <si>
     <t>Protocol File Path:</t>
@@ -97,7 +97,7 @@
     <t>Absorbance Endpoint</t>
   </si>
   <si>
-    <t>F1..F6</t>
+    <t>E1..F12</t>
   </si>
   <si>
     <t>Wavelengths:  600</t>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -172,7 +172,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,31 +193,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF5197CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60A0D1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8E9F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF428EC7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3385C2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F3FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7EB2DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF247CBD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF8DBCE0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F3FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF247CBD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7EB2DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABCEEA"/>
+        <fgColor rgb="FFBAD7EF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -249,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -286,14 +316,27 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -316,39 +359,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -400,7 +443,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -511,6 +554,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -519,13 +569,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -590,46 +633,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:O32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -637,7 +660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -645,12 +668,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -658,23 +681,23 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>45835</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
+        <v>45849</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>0.49559027777777781</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
+        <v>0.48841435185185184</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -682,7 +705,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -690,7 +713,7 @@
         <v>24011019</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -698,13 +721,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="4"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -712,12 +735,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -725,36 +748,36 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="4"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
       <c r="B22">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B24" s="5"/>
       <c r="C24" s="6">
         <v>1</v>
@@ -793,7 +816,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
         <v>25</v>
       </c>
@@ -813,7 +836,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>26</v>
       </c>
@@ -833,7 +856,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>27</v>
       </c>
@@ -853,7 +876,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
@@ -873,115 +896,115 @@
         <v>600</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
+      <c r="C29" s="9">
+        <v>1.9470000000000001</v>
+      </c>
+      <c r="D29" s="9">
+        <v>1.982</v>
+      </c>
+      <c r="E29" s="10">
+        <v>1.66</v>
+      </c>
+      <c r="F29" s="11">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="G29" s="12">
+        <v>2.0779999999999998</v>
+      </c>
+      <c r="H29" s="9">
+        <v>1.9330000000000001</v>
+      </c>
+      <c r="I29" s="13">
+        <v>2.2029999999999998</v>
+      </c>
+      <c r="J29" s="9">
+        <v>1.9119999999999999</v>
+      </c>
+      <c r="K29" s="13">
+        <v>2.1880000000000002</v>
+      </c>
+      <c r="L29" s="14">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="M29" s="14">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="N29" s="14">
+        <v>0.04</v>
+      </c>
       <c r="O29" s="8">
         <v>600</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="9">
-        <v>1.79</v>
-      </c>
-      <c r="D30" s="10">
-        <v>1.4810000000000001</v>
-      </c>
-      <c r="E30" s="11">
-        <v>2.1539999999999999</v>
-      </c>
-      <c r="F30" s="12">
-        <v>1.8280000000000001</v>
-      </c>
-      <c r="G30" s="10">
-        <v>1.5109999999999999</v>
-      </c>
-      <c r="H30" s="13">
-        <v>1.7110000000000001</v>
-      </c>
-      <c r="I30" s="11">
-        <v>2.1539999999999999</v>
-      </c>
-      <c r="J30" s="12">
-        <v>1.8280000000000001</v>
-      </c>
-      <c r="K30" s="10">
-        <v>1.5109999999999999</v>
-      </c>
-      <c r="L30" s="13">
-        <v>1.7110000000000001</v>
-      </c>
-      <c r="M30" s="11">
-        <v>2.1539999999999999</v>
-      </c>
-      <c r="N30" s="12">
-        <v>1.8280000000000001</v>
+      <c r="C30" s="14">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="D30" s="15">
+        <v>1.345</v>
+      </c>
+      <c r="E30" s="13">
+        <v>2.2589999999999999</v>
+      </c>
+      <c r="F30" s="13">
+        <v>2.1960000000000002</v>
+      </c>
+      <c r="G30" s="16">
+        <v>2.5419999999999998</v>
+      </c>
+      <c r="H30" s="16">
+        <v>2.512</v>
+      </c>
+      <c r="I30" s="15">
+        <v>1.3280000000000001</v>
+      </c>
+      <c r="J30" s="15">
+        <v>1.3089999999999999</v>
+      </c>
+      <c r="K30" s="17">
+        <v>1.1839999999999999</v>
+      </c>
+      <c r="L30" s="9">
+        <v>1.976</v>
+      </c>
+      <c r="M30" s="17">
+        <v>1.268</v>
+      </c>
+      <c r="N30" s="18">
+        <v>0.73599999999999999</v>
       </c>
       <c r="O30" s="8">
         <v>600</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="9">
-        <v>1.79</v>
-      </c>
-      <c r="D31" s="10">
-        <v>1.4810000000000001</v>
-      </c>
-      <c r="E31" s="11">
-        <v>2.1539999999999999</v>
-      </c>
-      <c r="F31" s="12">
-        <v>1.8280000000000001</v>
-      </c>
-      <c r="G31" s="10">
-        <v>1.5109999999999999</v>
-      </c>
-      <c r="H31" s="13">
-        <v>1.7110000000000001</v>
-      </c>
-      <c r="I31" s="11">
-        <v>2.1539999999999999</v>
-      </c>
-      <c r="J31" s="12">
-        <v>1.8280000000000001</v>
-      </c>
-      <c r="K31" s="10">
-        <v>1.5109999999999999</v>
-      </c>
-      <c r="L31" s="13">
-        <v>1.7110000000000001</v>
-      </c>
-      <c r="M31" s="11">
-        <v>2.1539999999999999</v>
-      </c>
-      <c r="N31" s="12">
-        <v>1.8280000000000001</v>
-      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
       <c r="O31" s="8">
         <v>600</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
         <v>32</v>
       </c>
@@ -1004,7 +1027,6 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>